--- a/docs/inventario_datasets.xlsx
+++ b/docs/inventario_datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gui30\OneDrive\Ambiente de Trabalho\dissertacao_anomalias\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E7B3D2-CA51-4097-B7F4-2E2A8A3776BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36643E16-59DA-413F-8678-4CA857ACAE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23372593-51CA-4EF6-8717-019FF2A6DA99}"/>
   </bookViews>
@@ -34,81 +34,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>dataset</t>
   </si>
   <si>
-    <t>dominio</t>
-  </si>
-  <si>
     <t>origem</t>
   </si>
   <si>
-    <t>formato</t>
-  </si>
-  <si>
-    <t>prioridade</t>
-  </si>
-  <si>
     <t>energia</t>
   </si>
   <si>
-    <t>github pedroccpimenta</t>
-  </si>
-  <si>
-    <t>zip/csv</t>
-  </si>
-  <si>
-    <t>alta</t>
-  </si>
-  <si>
-    <t>agua</t>
-  </si>
-  <si>
-    <t>meteo</t>
-  </si>
-  <si>
-    <t>média</t>
-  </si>
-  <si>
-    <t>stcp_autocarros</t>
-  </si>
-  <si>
-    <t>mobilidade</t>
-  </si>
-  <si>
-    <t>baixa</t>
-  </si>
-  <si>
-    <t>electricity_load_diagrams_2011_2014</t>
-  </si>
-  <si>
     <t>UCI</t>
   </si>
   <si>
-    <t>zip/txt ou csv</t>
-  </si>
-  <si>
-    <t>consumo_energia_15m_sql</t>
-  </si>
-  <si>
-    <t>zip/sql</t>
-  </si>
-  <si>
-    <t>consumo_agua_sql</t>
-  </si>
-  <si>
-    <t>consumo_energia_15m_nov2025</t>
-  </si>
-  <si>
-    <t>consumo_agua_nov2025</t>
-  </si>
-  <si>
-    <t>meteorologia_nov2025</t>
-  </si>
-  <si>
-    <t>zip</t>
+    <t>domínio</t>
+  </si>
+  <si>
+    <t>frequência</t>
+  </si>
+  <si>
+    <t>nº séries</t>
+  </si>
+  <si>
+    <t>período</t>
+  </si>
+  <si>
+    <t>observações</t>
+  </si>
+  <si>
+    <t>consumo15m</t>
+  </si>
+  <si>
+    <t>15 min</t>
+  </si>
+  <si>
+    <t>2022–2025</t>
+  </si>
+  <si>
+    <t>CMMaia</t>
+  </si>
+  <si>
+    <t>consumo elétrico</t>
+  </si>
+  <si>
+    <t>aqualog</t>
+  </si>
+  <si>
+    <t>água</t>
+  </si>
+  <si>
+    <t>irregular</t>
+  </si>
+  <si>
+    <t>~devices</t>
+  </si>
+  <si>
+    <t>dados de sensores</t>
+  </si>
+  <si>
+    <t>electricityload</t>
+  </si>
+  <si>
+    <t>2011–2014</t>
+  </si>
+  <si>
+    <t>benchmark</t>
   </si>
 </sst>
 </file>
@@ -144,13 +135,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -164,14 +186,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2048D80E-7010-43BD-A9F1-D37BA253C325}" name="Tabela1" displayName="Tabela1" ref="A1:E8" totalsRowShown="0">
-  <autoFilter ref="A1:E8" xr:uid="{2048D80E-7010-43BD-A9F1-D37BA253C325}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D35D208-BB04-4C17-8AE8-1ED7F9AC53F5}" name="dataset"/>
-    <tableColumn id="2" xr3:uid="{1AF5F299-90D0-493F-93F6-40BF9B783EA9}" name="dominio"/>
-    <tableColumn id="3" xr3:uid="{00200587-6E52-4FE3-B2BA-68A592788F84}" name="origem"/>
-    <tableColumn id="4" xr3:uid="{59FE3AFB-17A6-4663-B425-97944353E368}" name="formato"/>
-    <tableColumn id="5" xr3:uid="{78DDBE3D-2598-4259-A802-953D44FA9FB3}" name="prioridade"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D2C56F95-B533-48FE-860E-48AA34CD13C5}" name="Tabela1" displayName="Tabela1" ref="A1:G4" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:G4" xr:uid="{D2C56F95-B533-48FE-860E-48AA34CD13C5}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{BA1E2E33-F774-4CA2-9BBA-D1ED3F18B7F6}" name="dataset" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{A43615B1-8F65-40FA-9CDA-42F4C5636DA3}" name="domínio" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{AB40286D-3E69-44EA-B50B-058657CE1486}" name="frequência" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{6F3C745D-7C6B-4040-BC26-BD1066181975}" name="nº séries" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{D695F36E-BCFB-44AE-AC5F-07E0F3B5AD5D}" name="período" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{68162544-0D35-4272-B5C1-64396BC17465}" name="origem" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{888BE6CE-D693-451D-A1FB-3B3F0DEEB317}" name="observações" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -474,150 +498,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8F1EAD-512B-4375-AA70-5645CF0D5963}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="9.77734375" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
     <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
     <col min="8" max="8" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1">
+        <v>370</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="G4" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
